--- a/input/timetable/Физика.xlsx
+++ b/input/timetable/Физика.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="163">
   <si>
     <t>пара</t>
   </si>
@@ -77,6 +77,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -128,6 +131,18 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Веселов С.И.</t>
+  </si>
+  <si>
+    <t>Мухутдинова Д.Р.</t>
+  </si>
+  <si>
+    <t>Заводовский А.Г.</t>
+  </si>
+  <si>
+    <t>Алексеев М.М.</t>
+  </si>
+  <si>
     <t>Электричество и магнетизм, п/г 2, А316</t>
   </si>
   <si>
@@ -137,15 +152,33 @@
     <t>Электричество и магнетизм (лек), А314</t>
   </si>
   <si>
+    <t>Лебедев С.Л.</t>
+  </si>
+  <si>
+    <t>Голышева Н.Ф.</t>
+  </si>
+  <si>
+    <t>Шадрин Г.А.</t>
+  </si>
+  <si>
     <t>Геодезия (лек), А414</t>
   </si>
   <si>
     <t>Теоретическая механика и механика сплошных сред (лек), А329</t>
   </si>
   <si>
+    <t>Швец Е.С.</t>
+  </si>
+  <si>
     <t>602-31</t>
   </si>
   <si>
+    <t>Иванов А.В.</t>
+  </si>
+  <si>
+    <t>Логинов В.А.</t>
+  </si>
+  <si>
     <t>Линейная алгебра и аналитическая геометрия (лек), А305</t>
   </si>
   <si>
@@ -155,6 +188,18 @@
     <t>Основы экономической культуры (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Минникова Ю.М.</t>
+  </si>
+  <si>
+    <t>Кислова Н.А.</t>
+  </si>
+  <si>
+    <t>Кузнецов В.Е.</t>
+  </si>
+  <si>
+    <t>Макеев А.А.</t>
+  </si>
+  <si>
     <t>Общая и нефтепромысловая геология (лек), А329</t>
   </si>
   <si>
@@ -179,12 +224,21 @@
     <t>Линейная алгебра и аналитическая геометрия (пр), А305//</t>
   </si>
   <si>
+    <t>Семенов О.Ю.</t>
+  </si>
+  <si>
     <t>Информатика, п/г 1, У601</t>
   </si>
   <si>
     <t>Информатика, п/г 2, У601</t>
   </si>
   <si>
+    <t>Назина Н.Б.</t>
+  </si>
+  <si>
+    <t>Гореликов А.В.</t>
+  </si>
+  <si>
     <t>1-2.</t>
   </si>
   <si>
@@ -203,6 +257,9 @@
     <t>Оптические системы связи (пр), А329</t>
   </si>
   <si>
+    <t>Сысоев С.М.</t>
+  </si>
+  <si>
     <t>Датчики физических полей (лек), А329</t>
   </si>
   <si>
@@ -272,9 +329,24 @@
     <t>02.02.2026-10.04.2026</t>
   </si>
   <si>
+    <t>Грамма Д.В.; Логинов В.А.</t>
+  </si>
+  <si>
+    <t>Алексеев М.М./Логинов В.А.</t>
+  </si>
+  <si>
+    <t>Голышева Н.Ф.; Назина Н.Б.</t>
+  </si>
+  <si>
+    <t>Назина Н.Б.; Голышева Н.Ф.</t>
+  </si>
+  <si>
     <t>Основы предпринимательской деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Грамма Д.В.</t>
+  </si>
+  <si>
     <t>Молекулярная физика и термодинамика (лаб), А301</t>
   </si>
   <si>
@@ -293,12 +365,27 @@
     <t>Атомная и ядерная физика, п/г 1, А330</t>
   </si>
   <si>
+    <t>Солопий Д.К.; Лебедев С.Л.</t>
+  </si>
+  <si>
+    <t>Лебедев С.Л.; Солопий Д.К.</t>
+  </si>
+  <si>
+    <t>Коновалова Е.В.</t>
+  </si>
+  <si>
     <t>Линейные и нелинейные уравнения физики (лек), А329</t>
   </si>
   <si>
     <t>Линейные и нелинейные уравнения физики (пр), А329</t>
   </si>
   <si>
+    <t>Пешков А.А.</t>
+  </si>
+  <si>
+    <t>Воробьева А.Д.</t>
+  </si>
+  <si>
     <t>Информатика, п/г 1, У601//</t>
   </si>
   <si>
@@ -332,6 +419,9 @@
     <t>Геодезия, п/г 1, А414</t>
   </si>
   <si>
+    <t>Смирнова И.В.</t>
+  </si>
+  <si>
     <t>Иностранный язык (пр),  А501</t>
   </si>
   <si>
@@ -350,6 +440,9 @@
     <t>Молекулярная физика и термодинамика (пр)/(лек), А305</t>
   </si>
   <si>
+    <t>Логинов В.А./Семенов О.Ю.</t>
+  </si>
+  <si>
     <t>Теория вероятностей и математическая статистика (пр), А305</t>
   </si>
   <si>
@@ -365,6 +458,9 @@
     <t>Теория вероятностей и математическая статистика (лек), А305// Основы предпринимательской деятельности (пр), А305</t>
   </si>
   <si>
+    <t>Семенов О.Ю./Смирнова И.В.</t>
+  </si>
+  <si>
     <t>Газодинамические основы процессов разделения фаз (лек), А314</t>
   </si>
   <si>
@@ -398,9 +494,6 @@
     <t>Иностранный язык в профессиональной сфере (пр), А503</t>
   </si>
   <si>
-    <t>Учебная практика, научно-исследовательская работа, А305</t>
-  </si>
-  <si>
     <t>Интегральные уравнения и вариационное исчисление (пр), А329</t>
   </si>
   <si>
@@ -420,6 +513,9 @@
   </si>
   <si>
     <t>Тепломассообмен (пр), А329</t>
+  </si>
+  <si>
+    <t>Учебная практика, научно-исследовательская работа, А329</t>
   </si>
 </sst>
 </file>
@@ -531,7 +627,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,6 +646,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -561,7 +663,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="57">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -678,6 +780,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -809,6 +924,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1060,6 +1188,17 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -1281,7 +1420,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="256">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1321,28 +1460,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1367,38 +1509,41 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1409,408 +1554,419 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2121,7 +2277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2130,10 +2286,11 @@
     <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="21.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2141,15 +2298,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2157,39 +2314,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2199,35 +2356,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="75" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="99" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -2238,378 +2395,458 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="83"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="85"/>
-    </row>
-    <row r="11" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="106" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="107"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="109"/>
+      <c r="G10" s="77" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="69" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="71"/>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="93" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="94"/>
+      <c r="E11" s="94" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="95"/>
+      <c r="G11" s="78" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="86" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="88"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C12" s="110" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="102" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="115"/>
-      <c r="E13" s="116" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="104"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
+      <c r="C13" s="126" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="139"/>
+      <c r="E13" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="F13" s="128"/>
+      <c r="G13" s="80" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
         <v>5</v>
       </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="30">
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="76"/>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="31">
         <v>1</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="103" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="77" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>2</v>
+      </c>
+      <c r="C16" s="93" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="78" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>3</v>
+      </c>
+      <c r="C17" s="93" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="78" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="29">
+        <v>4</v>
+      </c>
+      <c r="C18" s="149" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="150"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="83" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="31">
+        <v>1</v>
+      </c>
+      <c r="C19" s="144" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="146"/>
+      <c r="G19" s="82" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>2</v>
+      </c>
+      <c r="C20" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="94"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>3</v>
+      </c>
+      <c r="C21" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="80" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+    </row>
+    <row r="22" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="29">
+        <v>4</v>
+      </c>
+      <c r="C22" s="96" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="97"/>
+      <c r="E22" s="97"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="84" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="33"/>
+      <c r="O22" s="33"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A23" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="31">
+        <v>1</v>
+      </c>
+      <c r="C23" s="90" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="82" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>2</v>
+      </c>
+      <c r="C24" s="93" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>3</v>
+      </c>
+      <c r="C25" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="78" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="32"/>
+      <c r="B26" s="29">
+        <v>4</v>
+      </c>
+      <c r="C26" s="153" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="155"/>
+      <c r="G26" s="79" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="31">
+        <v>1</v>
+      </c>
+      <c r="C27" s="147" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="148"/>
+      <c r="E27" s="115" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="116"/>
+      <c r="G27" s="77" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="27">
+        <v>2</v>
+      </c>
+      <c r="C28" s="113" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="152"/>
+      <c r="G28" s="78" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="27">
+        <v>3</v>
+      </c>
+      <c r="C29" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="78" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="67"/>
+      <c r="B30" s="68">
+        <v>4</v>
+      </c>
+      <c r="C30" s="141"/>
+      <c r="D30" s="142"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="83"/>
+    </row>
+    <row r="31" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="67"/>
+      <c r="B31" s="68">
+        <v>5</v>
+      </c>
+      <c r="C31" s="132" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="133"/>
+      <c r="E31" s="133"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="83" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A32" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="31">
+        <v>3</v>
+      </c>
+      <c r="C32" s="120"/>
+      <c r="D32" s="121"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="77"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="26"/>
+      <c r="B33" s="27">
+        <v>4</v>
+      </c>
+      <c r="C33" s="93" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="80" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="32"/>
+      <c r="B34" s="29">
+        <v>5</v>
+      </c>
+      <c r="C34" s="135"/>
+      <c r="D34" s="136"/>
+      <c r="E34" s="137" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="138"/>
+      <c r="G34" s="84" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="38"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="129"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="40"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="41"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="126"/>
+      <c r="D36" s="127"/>
+      <c r="E36" s="127"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="80"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="42"/>
+      <c r="B37" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="123" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="81" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="43"/>
+      <c r="B38" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="81"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>2</v>
-      </c>
-      <c r="C16" s="69" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-    </row>
-    <row r="17" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>3</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-    </row>
-    <row r="18" spans="1:14" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="28">
-        <v>4</v>
-      </c>
-      <c r="C18" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="126"/>
-      <c r="E18" s="126"/>
-      <c r="F18" s="127"/>
-    </row>
-    <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="30">
-        <v>1</v>
-      </c>
-      <c r="C19" s="120" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="122"/>
-    </row>
-    <row r="20" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>2</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="71"/>
-    </row>
-    <row r="21" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>3</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-    </row>
-    <row r="22" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="31"/>
-      <c r="B22" s="28">
-        <v>4</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="74"/>
-      <c r="I22" s="32"/>
-      <c r="N22" s="32"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A23" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="30">
-        <v>1</v>
-      </c>
-      <c r="C23" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="68"/>
-    </row>
-    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>2</v>
-      </c>
-      <c r="C24" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="71"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>3</v>
-      </c>
-      <c r="C25" s="69" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
-    </row>
-    <row r="26" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="31"/>
-      <c r="B26" s="28">
-        <v>4</v>
-      </c>
-      <c r="C26" s="129" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="131"/>
-    </row>
-    <row r="27" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="30">
-        <v>1</v>
-      </c>
-      <c r="C27" s="123" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="124"/>
-      <c r="E27" s="91" t="s">
-        <v>99</v>
-      </c>
-      <c r="F27" s="92"/>
-    </row>
-    <row r="28" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="26">
-        <v>2</v>
-      </c>
-      <c r="C28" s="89" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="128"/>
-    </row>
-    <row r="29" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="33"/>
-      <c r="B29" s="26">
-        <v>3</v>
-      </c>
-      <c r="C29" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71"/>
-    </row>
-    <row r="30" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="62"/>
-      <c r="B30" s="63">
-        <v>4</v>
-      </c>
-      <c r="C30" s="117"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
-    </row>
-    <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="62"/>
-      <c r="B31" s="63">
-        <v>5</v>
-      </c>
-      <c r="C31" s="108" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="110"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A32" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="30">
-        <v>3</v>
-      </c>
-      <c r="C32" s="96"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="98"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26">
-        <v>4</v>
-      </c>
-      <c r="C33" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71"/>
-    </row>
-    <row r="34" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="31"/>
-      <c r="B34" s="28">
-        <v>5</v>
-      </c>
-      <c r="C34" s="111"/>
-      <c r="D34" s="112"/>
-      <c r="E34" s="113" t="s">
-        <v>93</v>
-      </c>
-      <c r="F34" s="114"/>
-    </row>
-    <row r="35" spans="1:6" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="35"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="107"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="37"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="102"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="104"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="38"/>
-      <c r="B37" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" s="100"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="101"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="39"/>
-      <c r="B38" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="93" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="94"/>
-      <c r="E38" s="94"/>
-      <c r="F38" s="95"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="119"/>
+      <c r="G38" s="79" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>15</v>
       </c>
@@ -2677,7 +2914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2686,10 +2923,11 @@
     <col min="4" max="4" width="17.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2697,15 +2935,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2713,39 +2951,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2755,411 +2993,486 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="75" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="99" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="43"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="30">
+      <c r="D9" s="45"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="31">
         <v>1</v>
       </c>
-      <c r="C10" s="120" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="122"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="144" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="145"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="146"/>
+      <c r="G10" s="77" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="C11" s="126" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="80" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="159" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="80" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="159" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="161"/>
+      <c r="G13" s="73"/>
+    </row>
+    <row r="14" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="31">
+        <v>1</v>
+      </c>
+      <c r="C14" s="177"/>
+      <c r="D14" s="178"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="179"/>
+      <c r="G14" s="72"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
+        <v>2</v>
+      </c>
+      <c r="C15" s="113" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="78" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="171" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="172"/>
+      <c r="E16" s="172"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="78" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>4</v>
+      </c>
+      <c r="C17" s="165" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="166"/>
+      <c r="E17" s="166"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="104"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="29">
+        <v>5</v>
+      </c>
+      <c r="C18" s="174" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="175"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="176"/>
+      <c r="G18" s="84" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="31">
+        <v>1</v>
+      </c>
+      <c r="C19" s="90" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="89" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="25">
+        <v>2</v>
+      </c>
+      <c r="C20" s="162" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="163"/>
+      <c r="E20" s="163"/>
+      <c r="F20" s="164"/>
+      <c r="G20" s="78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="135" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="136"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="137"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="135" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="136"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="137"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="30">
+      <c r="C21" s="93" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="78" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
+        <v>4</v>
+      </c>
+      <c r="C22" s="110" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="78" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="32"/>
+      <c r="B23" s="29">
+        <v>5</v>
+      </c>
+      <c r="C23" s="168"/>
+      <c r="D23" s="169"/>
+      <c r="E23" s="169"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="78"/>
+    </row>
+    <row r="24" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="156"/>
-      <c r="D14" s="157"/>
-      <c r="E14" s="157"/>
-      <c r="F14" s="158"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="C24" s="180" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="181"/>
+      <c r="E24" s="181"/>
+      <c r="F24" s="182"/>
+      <c r="G24" s="82" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <v>2</v>
       </c>
-      <c r="C15" s="89" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="128"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C25" s="110" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="150" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="151"/>
-      <c r="E16" s="151"/>
-      <c r="F16" s="152"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C26" s="123" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="32"/>
+      <c r="B27" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="174" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="175"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="176"/>
+      <c r="G27" s="65"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="31">
+        <v>3</v>
+      </c>
+      <c r="C28" s="144" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="145"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="77" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="27">
         <v>4</v>
       </c>
-      <c r="C17" s="141" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="143"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="28">
+      <c r="C29" s="123" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="124"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="78" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="36"/>
+      <c r="B30" s="27">
         <v>5</v>
       </c>
-      <c r="C18" s="153" t="s">
+      <c r="C30" s="162" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="163"/>
+      <c r="E30" s="163"/>
+      <c r="F30" s="164"/>
+      <c r="G30" s="78" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="37"/>
+      <c r="B31" s="29">
+        <v>6</v>
+      </c>
+      <c r="C31" s="187" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" s="188"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="189"/>
+      <c r="G31" s="84" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="31">
+        <v>2</v>
+      </c>
+      <c r="C32" s="190" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="191"/>
+      <c r="E32" s="191"/>
+      <c r="F32" s="192"/>
+      <c r="G32" s="82" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="26"/>
+      <c r="B33" s="27">
+        <v>3</v>
+      </c>
+      <c r="C33" s="123" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="125"/>
+      <c r="G33" s="78" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="49"/>
+      <c r="B34" s="27">
+        <v>4</v>
+      </c>
+      <c r="C34" s="141"/>
+      <c r="D34" s="142"/>
+      <c r="E34" s="142"/>
+      <c r="F34" s="143"/>
+      <c r="G34" s="81"/>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="50"/>
+      <c r="B35" s="29">
+        <v>5</v>
+      </c>
+      <c r="C35" s="156"/>
+      <c r="D35" s="157"/>
+      <c r="E35" s="157"/>
+      <c r="F35" s="158"/>
+      <c r="G35" s="65"/>
+    </row>
+    <row r="36" spans="1:7" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="57"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="196"/>
+      <c r="D36" s="197"/>
+      <c r="E36" s="197"/>
+      <c r="F36" s="198"/>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="51"/>
+      <c r="B37" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="193" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="154"/>
-      <c r="E18" s="154"/>
-      <c r="F18" s="155"/>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="30">
-        <v>1</v>
-      </c>
-      <c r="C19" s="144"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="146"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="24">
-        <v>2</v>
-      </c>
-      <c r="C20" s="138" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139"/>
-      <c r="F20" s="140"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>3</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
-        <v>4</v>
-      </c>
-      <c r="C22" s="86" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="87"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="88"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="31"/>
-      <c r="B23" s="28">
-        <v>5</v>
-      </c>
-      <c r="C23" s="147" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="149"/>
-    </row>
-    <row r="24" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="30">
-        <v>1</v>
-      </c>
-      <c r="C24" s="159" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="160"/>
-      <c r="E24" s="160"/>
-      <c r="F24" s="161"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>2</v>
-      </c>
-      <c r="C25" s="86" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="88"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
-        <v>3</v>
-      </c>
-      <c r="C26" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="101"/>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="31"/>
-      <c r="B27" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="153" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="155"/>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="30">
-        <v>3</v>
-      </c>
-      <c r="C28" s="120" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="121"/>
-      <c r="E28" s="121"/>
-      <c r="F28" s="122"/>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="33"/>
-      <c r="B29" s="26">
-        <v>4</v>
-      </c>
-      <c r="C29" s="99" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100"/>
-      <c r="F29" s="101"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="33"/>
-      <c r="B30" s="26">
-        <v>5</v>
-      </c>
-      <c r="C30" s="138" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="140"/>
-    </row>
-    <row r="31" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="34"/>
-      <c r="B31" s="28">
-        <v>6</v>
-      </c>
-      <c r="C31" s="166" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="167"/>
-      <c r="E31" s="167"/>
-      <c r="F31" s="168"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="30">
-        <v>2</v>
-      </c>
-      <c r="C32" s="169" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" s="170"/>
-      <c r="E32" s="170"/>
-      <c r="F32" s="171"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="25"/>
-      <c r="B33" s="26">
-        <v>3</v>
-      </c>
-      <c r="C33" s="99" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="101"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="45"/>
-      <c r="B34" s="26">
-        <v>4</v>
-      </c>
-      <c r="C34" s="117"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="119"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="46"/>
-      <c r="B35" s="28">
-        <v>5</v>
-      </c>
-      <c r="C35" s="132"/>
-      <c r="D35" s="133"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="134"/>
-    </row>
-    <row r="36" spans="1:6" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="53"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="175"/>
-      <c r="D36" s="176"/>
-      <c r="E36" s="176"/>
-      <c r="F36" s="177"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="47"/>
-      <c r="B37" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="172" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="173"/>
-      <c r="E37" s="173"/>
-      <c r="F37" s="174"/>
-    </row>
-    <row r="38" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="52"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="163"/>
-      <c r="D38" s="164"/>
-      <c r="E38" s="164"/>
-      <c r="F38" s="165"/>
-    </row>
-    <row r="39" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="65"/>
-      <c r="C39" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="162"/>
-      <c r="E39" s="162"/>
-      <c r="F39" s="162"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="77" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="56"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="184"/>
+      <c r="D38" s="185"/>
+      <c r="E38" s="185"/>
+      <c r="F38" s="186"/>
+      <c r="G38" s="73"/>
+    </row>
+    <row r="39" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="71"/>
+      <c r="C39" s="183" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="183"/>
+      <c r="E39" s="183"/>
+      <c r="F39" s="183"/>
+      <c r="G39" s="69"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>15</v>
       </c>
@@ -3222,7 +3535,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3231,12 +3544,13 @@
     <col min="4" max="4" width="18.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="9.7109375" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="9" max="9" width="9.7109375" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3244,15 +3558,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3260,39 +3574,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3302,35 +3616,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="75" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+      <c r="C8" s="99" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -3341,340 +3655,409 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="25">
         <v>4</v>
       </c>
-      <c r="C10" s="197" t="s">
+      <c r="C10" s="218" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="219"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="220"/>
+      <c r="G10" s="77" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
+        <v>5</v>
+      </c>
+      <c r="C11" s="221" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="222"/>
+      <c r="E11" s="222"/>
+      <c r="F11" s="223"/>
+      <c r="G11" s="78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>7</v>
+      </c>
+      <c r="C12" s="113" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="114"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="152"/>
+      <c r="G12" s="78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
+        <v>8</v>
+      </c>
+      <c r="C13" s="168" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="169"/>
+      <c r="E13" s="169"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="84" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="31">
+        <v>3</v>
+      </c>
+      <c r="C14" s="208"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="77"/>
+    </row>
+    <row r="15" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="25">
+        <v>4</v>
+      </c>
+      <c r="C15" s="113" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" s="152"/>
+      <c r="G15" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="198"/>
-      <c r="E10" s="198"/>
-      <c r="F10" s="199"/>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+    </row>
+    <row r="16" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <v>5</v>
       </c>
-      <c r="C11" s="200" t="s">
+      <c r="C16" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="152"/>
+      <c r="G16" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="201"/>
-      <c r="E11" s="201"/>
-      <c r="F11" s="202"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="32"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="215"/>
+      <c r="D17" s="216"/>
+      <c r="E17" s="216"/>
+      <c r="F17" s="217"/>
+      <c r="G17" s="87"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="31">
+        <v>2</v>
+      </c>
+      <c r="C18" s="218" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="219"/>
+      <c r="E18" s="219"/>
+      <c r="F18" s="220"/>
+      <c r="G18" s="82" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
+        <v>3</v>
+      </c>
+      <c r="C19" s="93" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="81" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <v>7</v>
       </c>
-      <c r="C12" s="89" t="s">
+      <c r="C20" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="213"/>
+      <c r="E20" s="213"/>
+      <c r="F20" s="214"/>
+      <c r="G20" s="86" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="32"/>
+      <c r="B21" s="29">
+        <v>6</v>
+      </c>
+      <c r="C21" s="227" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="228"/>
+      <c r="E21" s="228"/>
+      <c r="F21" s="229"/>
+      <c r="G21" s="79" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="31">
+        <v>2</v>
+      </c>
+      <c r="C22" s="230" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="231"/>
+      <c r="E22" s="231"/>
+      <c r="F22" s="232"/>
+      <c r="G22" s="88" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
+        <v>3</v>
+      </c>
+      <c r="C23" s="221" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="222"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="223"/>
+      <c r="G23" s="78" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>4</v>
+      </c>
+      <c r="C24" s="212" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="213"/>
+      <c r="E24" s="213"/>
+      <c r="F24" s="214"/>
+      <c r="G24" s="86" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="32"/>
+      <c r="B25" s="29">
+        <v>5</v>
+      </c>
+      <c r="C25" s="205" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="206"/>
+      <c r="E25" s="206"/>
+      <c r="F25" s="207"/>
+      <c r="G25" s="87" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="208" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="115"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="116"/>
+      <c r="G26" s="34"/>
+    </row>
+    <row r="27" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="210"/>
+      <c r="E27" s="210"/>
+      <c r="F27" s="211"/>
+      <c r="G27" s="86"/>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="27">
+        <v>7</v>
+      </c>
+      <c r="C28" s="110" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="112"/>
+      <c r="G28" s="78" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="37"/>
+      <c r="B29" s="29">
+        <v>8</v>
+      </c>
+      <c r="C29" s="174" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="175"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="176"/>
+      <c r="G29" s="84" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="31">
+        <v>1</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="77" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="52"/>
+      <c r="B31" s="27">
+        <v>2</v>
+      </c>
+      <c r="C31" s="126" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="127"/>
+      <c r="E31" s="127"/>
+      <c r="F31" s="128"/>
+      <c r="G31" s="78" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="62"/>
+      <c r="B32" s="29">
+        <v>3</v>
+      </c>
+      <c r="C32" s="199"/>
+      <c r="D32" s="200"/>
+      <c r="E32" s="200"/>
+      <c r="F32" s="201"/>
+      <c r="G32" s="73"/>
+    </row>
+    <row r="33" spans="1:7" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="63"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="224"/>
+      <c r="D33" s="225"/>
+      <c r="E33" s="225"/>
+      <c r="F33" s="226"/>
+      <c r="G33" s="75"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="59"/>
+      <c r="B34" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="202" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="203"/>
+      <c r="E34" s="203"/>
+      <c r="F34" s="204"/>
+      <c r="G34" s="78" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="71"/>
+      <c r="C35" s="183" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="128"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
-        <v>8</v>
-      </c>
-      <c r="C13" s="147" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="148"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="149"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="30">
-        <v>3</v>
-      </c>
-      <c r="C14" s="187"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="92"/>
-    </row>
-    <row r="15" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="24">
-        <v>4</v>
-      </c>
-      <c r="C15" s="89" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90" t="s">
-        <v>114</v>
-      </c>
-      <c r="F15" s="128"/>
-    </row>
-    <row r="16" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>5</v>
-      </c>
-      <c r="C16" s="89" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="128"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="31"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="194"/>
-      <c r="D17" s="195"/>
-      <c r="E17" s="195"/>
-      <c r="F17" s="196"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="30">
-        <v>2</v>
-      </c>
-      <c r="C18" s="197" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="198"/>
-      <c r="E18" s="198"/>
-      <c r="F18" s="199"/>
-    </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
-        <v>3</v>
-      </c>
-      <c r="C19" s="69" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="71"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>7</v>
-      </c>
-      <c r="C20" s="191" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="192"/>
-      <c r="E20" s="192"/>
-      <c r="F20" s="193"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="31"/>
-      <c r="B21" s="28">
-        <v>6</v>
-      </c>
-      <c r="C21" s="206" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
-      <c r="F21" s="208"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="30">
-        <v>2</v>
-      </c>
-      <c r="C22" s="209" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="210"/>
-      <c r="E22" s="210"/>
-      <c r="F22" s="211"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
-        <v>3</v>
-      </c>
-      <c r="C23" s="200" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="201"/>
-      <c r="E23" s="201"/>
-      <c r="F23" s="202"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>4</v>
-      </c>
-      <c r="C24" s="191" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="192"/>
-      <c r="E24" s="192"/>
-      <c r="F24" s="193"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="31"/>
-      <c r="B25" s="28">
-        <v>5</v>
-      </c>
-      <c r="C25" s="184" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="185"/>
-      <c r="E25" s="185"/>
-      <c r="F25" s="186"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="187" t="s">
-        <v>53</v>
-      </c>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="92"/>
-    </row>
-    <row r="27" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="33"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="188"/>
-      <c r="D27" s="189"/>
-      <c r="E27" s="189"/>
-      <c r="F27" s="190"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="33"/>
-      <c r="B28" s="26">
-        <v>7</v>
-      </c>
-      <c r="C28" s="86" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="87"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="88"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="34"/>
-      <c r="B29" s="28">
-        <v>8</v>
-      </c>
-      <c r="C29" s="153" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="154"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="155"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="30">
-        <v>1</v>
-      </c>
-      <c r="C30" s="120" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="121"/>
-      <c r="E30" s="121"/>
-      <c r="F30" s="122"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="48"/>
-      <c r="B31" s="26">
-        <v>2</v>
-      </c>
-      <c r="C31" s="102" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="104"/>
-    </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="58"/>
-      <c r="B32" s="28">
-        <v>3</v>
-      </c>
-      <c r="C32" s="178"/>
-      <c r="D32" s="179"/>
-      <c r="E32" s="179"/>
-      <c r="F32" s="180"/>
-    </row>
-    <row r="33" spans="1:6" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="59"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="203"/>
-      <c r="D33" s="204"/>
-      <c r="E33" s="204"/>
-      <c r="F33" s="205"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="55"/>
-      <c r="B34" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="181" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="182"/>
-      <c r="E34" s="182"/>
-      <c r="F34" s="183"/>
-    </row>
-    <row r="35" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="65"/>
-      <c r="C35" s="162" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="162"/>
-      <c r="E35" s="162"/>
-      <c r="F35" s="162"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D35" s="183"/>
+      <c r="E35" s="183"/>
+      <c r="F35" s="183"/>
+      <c r="G35" s="69"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="61"/>
+      <c r="C36" s="66"/>
       <c r="D36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="61"/>
+      <c r="C37" s="66"/>
       <c r="D37" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -3729,7 +4112,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3737,10 +4120,11 @@
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3748,15 +4132,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3764,39 +4148,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3806,368 +4190,435 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="75" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="75"/>
-      <c r="E9" s="51"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>33</v>
+      </c>
+      <c r="C9" s="99" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="99"/>
+      <c r="E9" s="55"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="43"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="D10" s="45"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="82" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="233"/>
-      <c r="E11" s="233"/>
-      <c r="F11" s="234"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="106" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="254"/>
+      <c r="E11" s="254"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="82" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="126" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="123" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="81" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
+        <v>5</v>
+      </c>
+      <c r="C14" s="123" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="79" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="31">
+        <v>2</v>
+      </c>
+      <c r="C15" s="251" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="252"/>
+      <c r="E15" s="252"/>
+      <c r="F15" s="253"/>
+      <c r="G15" s="82" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="242" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="244"/>
+      <c r="G16" s="81" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>4</v>
+      </c>
+      <c r="C17" s="245"/>
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="81"/>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="29">
+        <v>5</v>
+      </c>
+      <c r="C18" s="141"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="35"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="31">
+        <v>2</v>
+      </c>
+      <c r="C19" s="248"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="249"/>
+      <c r="F19" s="250"/>
+      <c r="G19" s="82"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>3</v>
+      </c>
+      <c r="C20" s="141"/>
+      <c r="D20" s="142"/>
+      <c r="E20" s="142"/>
+      <c r="F20" s="143"/>
+      <c r="G20" s="81"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>4</v>
+      </c>
+      <c r="C21" s="123" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="81" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
+        <v>5</v>
+      </c>
+      <c r="C22" s="126" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="81" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="32"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="102"/>
+      <c r="G23" s="35"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="31">
+        <v>2</v>
+      </c>
+      <c r="C24" s="144" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="145"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="82" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>3</v>
+      </c>
+      <c r="C25" s="126" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="81" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
+        <v>4</v>
+      </c>
+      <c r="C26" s="242" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="243"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="244"/>
+      <c r="G26" s="81" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="32"/>
+      <c r="B27" s="29">
+        <v>5</v>
+      </c>
+      <c r="C27" s="233" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="234"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="235"/>
+      <c r="G27" s="79" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="31">
+        <v>2</v>
+      </c>
+      <c r="C28" s="236" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="237"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="238"/>
+      <c r="G28" s="82" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="27">
+        <v>3</v>
+      </c>
+      <c r="C29" s="126" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="104"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="36"/>
+      <c r="B30" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
+      <c r="C30" s="123" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="124"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="81" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="37"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="184"/>
+      <c r="D31" s="185"/>
+      <c r="E31" s="185"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="35"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="25">
+        <v>2</v>
+      </c>
+      <c r="C32" s="239" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="240"/>
+      <c r="E32" s="240"/>
+      <c r="F32" s="241"/>
+      <c r="G32" s="85" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="52"/>
+      <c r="B33" s="27">
+        <v>3</v>
+      </c>
+      <c r="C33" s="123" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" s="124"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="125"/>
+      <c r="G33" s="81" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="52"/>
+      <c r="B34" s="27">
+        <v>4</v>
+      </c>
+      <c r="C34" s="123" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" s="124"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="81" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="52"/>
+      <c r="B35" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="99" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="101"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="30">
-        <v>2</v>
-      </c>
-      <c r="C15" s="230" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="231"/>
-      <c r="E15" s="231"/>
-      <c r="F15" s="232"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>3</v>
-      </c>
-      <c r="C16" s="221" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="222"/>
-      <c r="E16" s="222"/>
-      <c r="F16" s="223"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>4</v>
-      </c>
-      <c r="C17" s="224"/>
-      <c r="D17" s="225"/>
-      <c r="E17" s="225"/>
-      <c r="F17" s="226"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="28">
-        <v>5</v>
-      </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="30">
-        <v>2</v>
-      </c>
-      <c r="C19" s="227"/>
-      <c r="D19" s="228"/>
-      <c r="E19" s="228"/>
-      <c r="F19" s="229"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>3</v>
-      </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="119"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>4</v>
-      </c>
-      <c r="C21" s="99" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="100"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="101"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
-        <v>5</v>
-      </c>
-      <c r="C22" s="102" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="104"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="31"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="78"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="30">
-        <v>2</v>
-      </c>
-      <c r="C24" s="120" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="121"/>
-      <c r="E24" s="121"/>
-      <c r="F24" s="122"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>3</v>
-      </c>
-      <c r="C25" s="102" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="104"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
-        <v>4</v>
-      </c>
-      <c r="C26" s="221" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="222"/>
-      <c r="E26" s="222"/>
-      <c r="F26" s="223"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="31"/>
-      <c r="B27" s="28">
-        <v>5</v>
-      </c>
-      <c r="C27" s="212" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="213"/>
-      <c r="E27" s="213"/>
-      <c r="F27" s="214"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="30">
-        <v>2</v>
-      </c>
-      <c r="C28" s="215" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="216"/>
-      <c r="E28" s="216"/>
-      <c r="F28" s="217"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="33"/>
-      <c r="B29" s="26">
-        <v>3</v>
-      </c>
-      <c r="C29" s="102" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="103"/>
-      <c r="E29" s="103"/>
-      <c r="F29" s="104"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="33"/>
-      <c r="B30" s="26">
-        <v>4</v>
-      </c>
-      <c r="C30" s="99" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="101"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="34"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="163"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="165"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="24">
-        <v>2</v>
-      </c>
-      <c r="C32" s="218" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="219"/>
-      <c r="E32" s="219"/>
-      <c r="F32" s="220"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="48"/>
-      <c r="B33" s="26">
-        <v>3</v>
-      </c>
-      <c r="C33" s="99" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="101"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="48"/>
-      <c r="B34" s="26">
-        <v>4</v>
-      </c>
-      <c r="C34" s="99" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="101"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="48"/>
-      <c r="B35" s="26">
-        <v>5</v>
-      </c>
-      <c r="C35" s="99" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" s="100"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="101"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="49"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="163"/>
-      <c r="D36" s="164"/>
-      <c r="E36" s="164"/>
-      <c r="F36" s="165"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C35" s="123" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="124"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="81" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="53"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="184"/>
+      <c r="D36" s="185"/>
+      <c r="E36" s="185"/>
+      <c r="F36" s="186"/>
+      <c r="G36" s="35"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
